--- a/tabela de habitat.xlsx
+++ b/tabela de habitat.xlsx
@@ -1,27 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_rebio23-mxr/mxr23_Q/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_B99231274FC9658F1244B2F15FFF14A32A997546" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55090DFC-2DE6-4A77-9B38-EAFCE1CC1DB7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
-    <sheet name="tabela_final" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tabela_final" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="282">
   <si>
     <t>Variable</t>
   </si>
@@ -444,13 +437,437 @@
   </si>
   <si>
     <t>15 (5-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.Temp.C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8 (24.9-27.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5 (25.3-27.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2 (24.9-25.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8 (27-28.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9 (26.6-27.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3 (26.2-26.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.DO.mg.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1 (7.8-8.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5 (7.2-7.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9 (7.7-8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5 (6.5-8.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9 (7.8-7.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4 (4.9-6.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.Cond.uS.cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.4 (134-164.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.3 (134.1-156.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129 (98.3-160.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.6 (158.8-161.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.3 (161.2-165.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.3 (149.7-157.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.Turb.ntu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4 (4.6-10.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1 (2.1-14.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4 (1.5-9.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4 (6.1-6.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5 (17.2-17.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6 (24.2-34.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.pH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 (6.3-7.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8 (5.9-7.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5 (4.6-6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9 (5.9-6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6 (6.6-6.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9 (6.6-7.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.Elev.m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.1 (107.1-107.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.8 (112.8-112.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89 (89-89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1 (89.1-89.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71 (71-71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5 (41.5-41.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.Vel.m.s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (0-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.035 (0.035-0.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.073 (0.022-0.108)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.038 (0-0.115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293 (0.25-0.348)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022 (0.022-0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.Slope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (1-1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 (2.5-2.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2 (1.5-2.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (2-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7 (2-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 (1-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.Depth.max.cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (16-16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3 (29-31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7 (20-26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 (38-56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 (20-22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 (47-47)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.Depth.avg.cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7 (13.7-13.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 (20.3-28.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7 (16-22.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2 (30-51.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8 (15-19.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7 (40.7-40.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.Depth.mar.cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 (30-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7 (15-42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7 (22-87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (20-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3 (38-52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.Width.m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6 (3.6-3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7 (2.3-4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7 (1.1-2.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4 (2-14.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (0.8-1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2 (7.2-7.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s.Mud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 (100-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 (90-90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 (20-80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 (60-80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 (20-50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s.Sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (10-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 (20-80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 (20-40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 (50-80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Macrophytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (5-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (0-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8 (22.5-60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7 (0-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (0-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2 (20-50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7 (1-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Subm.veg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3 (5-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 (0-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 (0-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7 (10-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (0-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Overh.veg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7 (80-85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 (80-90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3 (0-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Leaf.l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7 (1-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 (5-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7 (20-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3 (1-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Algae.f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7 (1-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7 (0-50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Algae.a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3 (1-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7 (0-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Root.masses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (5-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.7 (50-90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Debris.l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7 (5-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7 (10-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h.Debris.s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7 (0-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (5-20)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -776,583 +1193,583 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>146</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>208</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>212</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>216</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>226</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>228</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
+        <v>229</v>
       </c>
       <c r="G13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>232</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>232</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>234</v>
       </c>
       <c r="F14" t="s">
-        <v>94</v>
+        <v>235</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>239</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>240</v>
       </c>
       <c r="G15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>242</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>244</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>245</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="G17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>253</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>254</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>255</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>233</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>258</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="F19" t="s">
-        <v>94</v>
+        <v>235</v>
       </c>
       <c r="G19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>261</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="G20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>267</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>268</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>269</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>270</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>271</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>272</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="G22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
       <c r="E23" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="F23" t="s">
-        <v>134</v>
+        <v>275</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>276</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>278</v>
       </c>
       <c r="F24" t="s">
-        <v>112</v>
+        <v>253</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>280</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>281</v>
       </c>
       <c r="F25" t="s">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="G25" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -1362,11 +1779,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E388249A-FA73-4EDC-9E0A-027AEB803D98}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +1806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1412,7 +1829,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1435,7 +1852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1458,7 +1875,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1481,7 +1898,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1504,7 +1921,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1527,7 +1944,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1550,7 +1967,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -1573,7 +1990,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -1596,7 +2013,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -1619,7 +2036,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -1642,7 +2059,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" t="s">
         <v>83</v>
       </c>
@@ -1665,7 +2082,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -1688,7 +2105,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -1711,7 +2128,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -1734,7 +2151,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -1757,7 +2174,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -1780,7 +2197,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" t="s">
         <v>116</v>
       </c>
@@ -1803,7 +2220,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" t="s">
         <v>120</v>
       </c>
@@ -1826,7 +2243,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -1849,7 +2266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" t="s">
         <v>128</v>
       </c>
@@ -1872,7 +2289,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" t="s">
         <v>132</v>
       </c>
@@ -1895,7 +2312,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" t="s">
         <v>135</v>
       </c>
@@ -1918,7 +2335,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" t="s">
         <v>138</v>
       </c>
@@ -1943,5 +2360,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/tabela de habitat.xlsx
+++ b/tabela de habitat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_rebio23-mxr/mxr23_Q/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_E8FA0B9960DD2A79F7007CD708813A554CA11F24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C49B060-9CE3-4541-97B1-5CFEBCB0E9F0}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_09FA781D42CFBA99372140D0B83CDD583E7D1A6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6B82422-BFB9-42BE-AEFC-4956D10ACF0E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="279">
   <si>
     <t>Variable</t>
   </si>
@@ -332,6 +332,120 @@
     <t>3.7 (0-10)</t>
   </si>
   <si>
+    <t>14.6 (14.6-14.6)</t>
+  </si>
+  <si>
+    <t>80 (80-80)</t>
+  </si>
+  <si>
+    <t>16.7 (15-20)</t>
+  </si>
+  <si>
+    <t>Site 1</t>
+  </si>
+  <si>
+    <t>Site 2</t>
+  </si>
+  <si>
+    <t>Site 3</t>
+  </si>
+  <si>
+    <t>Site 4</t>
+  </si>
+  <si>
+    <t>Site 5</t>
+  </si>
+  <si>
+    <t>Site 6</t>
+  </si>
+  <si>
+    <t>Water quality</t>
+  </si>
+  <si>
+    <t>Dissolved oxigen (mg/L)</t>
+  </si>
+  <si>
+    <t>Conductivity (uS/cm)</t>
+  </si>
+  <si>
+    <t>Turbidity (NTU)</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>Morphology</t>
+  </si>
+  <si>
+    <t>Elevation (m a.s.l.)</t>
+  </si>
+  <si>
+    <t>Water velocity (m/s)</t>
+  </si>
+  <si>
+    <t>Slope</t>
+  </si>
+  <si>
+    <t>Maximum depth (cm)</t>
+  </si>
+  <si>
+    <t>Average depth (cm)</t>
+  </si>
+  <si>
+    <t>Marginal depth (cm)</t>
+  </si>
+  <si>
+    <t>Width (m)</t>
+  </si>
+  <si>
+    <t>Substrate composition (%)</t>
+  </si>
+  <si>
+    <t>Mud</t>
+  </si>
+  <si>
+    <t>Sand</t>
+  </si>
+  <si>
+    <t>Habitat structures (%)</t>
+  </si>
+  <si>
+    <t>Aquatic macrophytes</t>
+  </si>
+  <si>
+    <t>Littoral grass</t>
+  </si>
+  <si>
+    <t>Submerged vegetation</t>
+  </si>
+  <si>
+    <t>Overhanging vegetation</t>
+  </si>
+  <si>
+    <t>Leaf litter</t>
+  </si>
+  <si>
+    <t>Fillamentous algae</t>
+  </si>
+  <si>
+    <t>Attached algae</t>
+  </si>
+  <si>
+    <t>Root masses</t>
+  </si>
+  <si>
+    <t>Small debris</t>
+  </si>
+  <si>
+    <t>Large debris</t>
+  </si>
+  <si>
+    <t>Temperature (°C)</t>
+  </si>
+  <si>
+    <t>7.0 (6.3-7.5)</t>
+  </si>
+  <si>
     <t>Variable</t>
   </si>
   <si>
@@ -482,15 +596,18 @@
     <t>m.Vel.m.s</t>
   </si>
   <si>
+    <t>0.017 (0-0.025)</t>
+  </si>
+  <si>
+    <t>0.035 (0.035-0.035)</t>
+  </si>
+  <si>
+    <t>0.073 (0.022-0.108)</t>
+  </si>
+  <si>
     <t>0 (0-0)</t>
   </si>
   <si>
-    <t>0.035 (0.035-0.035)</t>
-  </si>
-  <si>
-    <t>0.073 (0.022-0.108)</t>
-  </si>
-  <si>
     <t>0.293 (0.25-0.348)</t>
   </si>
   <si>
@@ -590,6 +707,9 @@
     <t>1.7 (1.1-2.1)</t>
   </si>
   <si>
+    <t>14.6 (14.6-14.6)</t>
+  </si>
+  <si>
     <t>1.2 (0.8-1.6)</t>
   </si>
   <si>
@@ -605,6 +725,9 @@
     <t>90 (90-90)</t>
   </si>
   <si>
+    <t>80 (80-80)</t>
+  </si>
+  <si>
     <t>70 (60-80)</t>
   </si>
   <si>
@@ -710,6 +833,9 @@
     <t>2.3 (1-5)</t>
   </si>
   <si>
+    <t>16.7 (15-20)</t>
+  </si>
+  <si>
     <t>h.Root.masses</t>
   </si>
   <si>
@@ -732,136 +858,16 @@
   </si>
   <si>
     <t>3.7 (0-10)</t>
-  </si>
-  <si>
-    <t>14.6 (14.6-14.6)</t>
-  </si>
-  <si>
-    <t>80 (80-80)</t>
-  </si>
-  <si>
-    <t>16.7 (15-20)</t>
-  </si>
-  <si>
-    <t>Site 1</t>
-  </si>
-  <si>
-    <t>Site 2</t>
-  </si>
-  <si>
-    <t>Site 3</t>
-  </si>
-  <si>
-    <t>Site 4</t>
-  </si>
-  <si>
-    <t>Site 5</t>
-  </si>
-  <si>
-    <t>Site 6</t>
-  </si>
-  <si>
-    <t>Water quality</t>
-  </si>
-  <si>
-    <t>Dissolved oxigen (mg/L)</t>
-  </si>
-  <si>
-    <t>Conductivity (uS/cm)</t>
-  </si>
-  <si>
-    <t>Turbidity (NTU)</t>
-  </si>
-  <si>
-    <t>pH</t>
-  </si>
-  <si>
-    <t>Morphology</t>
-  </si>
-  <si>
-    <t>Elevation (m a.s.l.)</t>
-  </si>
-  <si>
-    <t>Water velocity (m/s)</t>
-  </si>
-  <si>
-    <t>Slope</t>
-  </si>
-  <si>
-    <t>Maximum depth (cm)</t>
-  </si>
-  <si>
-    <t>Average depth (cm)</t>
-  </si>
-  <si>
-    <t>Marginal depth (cm)</t>
-  </si>
-  <si>
-    <t>Width (m)</t>
-  </si>
-  <si>
-    <t>Substrate composition (%)</t>
-  </si>
-  <si>
-    <t>Mud</t>
-  </si>
-  <si>
-    <t>Sand</t>
-  </si>
-  <si>
-    <t>Habitat structures (%)</t>
-  </si>
-  <si>
-    <t>Aquatic macrophytes</t>
-  </si>
-  <si>
-    <t>Littoral grass</t>
-  </si>
-  <si>
-    <t>Submerged vegetation</t>
-  </si>
-  <si>
-    <t>Overhanging vegetation</t>
-  </si>
-  <si>
-    <t>Leaf litter</t>
-  </si>
-  <si>
-    <t>Fillamentous algae</t>
-  </si>
-  <si>
-    <t>Attached algae</t>
-  </si>
-  <si>
-    <t>Root masses</t>
-  </si>
-  <si>
-    <t>Small debris</t>
-  </si>
-  <si>
-    <t>Large debris</t>
-  </si>
-  <si>
-    <t>Temperature (°C)</t>
-  </si>
-  <si>
-    <t>7.0 (6.3-7.5)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -904,10 +910,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1194,577 +1196,577 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="G1" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="F2" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="G2" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="F4" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="F8" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="G9" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="F10" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="E11" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="G11" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="D12" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="F12" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="F13" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="D14" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F14" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="G14" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="F15" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="G15" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="F16" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="G16" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="E17" t="s">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="F17" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="G17" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="C18" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="D18" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="E18" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="F18" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="G18" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="D19" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="E19" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="F19" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="G19" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="B20" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="E20" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="F20" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="G20" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D21" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="E21" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="F21" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="G21" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="B22" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="C22" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="E22" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F22" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="G22" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="D23" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="F23" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="G23" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="E24" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="F24" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="G24" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="D25" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="E25" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="F25" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="G25" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -1783,32 +1785,32 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
-        <v>242</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
-        <v>243</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s">
-        <v>244</v>
+        <v>110</v>
       </c>
       <c r="G1" t="s">
-        <v>245</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>246</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>273</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -1831,7 +1833,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1854,7 +1856,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>248</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1877,7 +1879,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -1900,10 +1902,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>250</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -1923,12 +1925,12 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
@@ -1951,7 +1953,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>258</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
         <v>64</v>
@@ -1963,7 +1965,7 @@
         <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>237</v>
+        <v>103</v>
       </c>
       <c r="F10" t="s">
         <v>67</v>
@@ -1974,10 +1976,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>253</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>
@@ -1997,7 +1999,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -2020,7 +2022,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>255</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
@@ -2043,7 +2045,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
@@ -2066,7 +2068,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>257</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -2089,12 +2091,12 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>259</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
         <v>69</v>
@@ -2106,7 +2108,7 @@
         <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>238</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
         <v>71</v>
@@ -2117,7 +2119,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -2140,12 +2142,12 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>262</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
         <v>76</v>
@@ -2168,7 +2170,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>264</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
@@ -2191,7 +2193,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>265</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
         <v>76</v>
@@ -2214,7 +2216,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>266</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s">
         <v>70</v>
@@ -2237,7 +2239,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>267</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
         <v>73</v>
@@ -2260,7 +2262,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
@@ -2283,7 +2285,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
         <v>76</v>
@@ -2295,7 +2297,7 @@
         <v>97</v>
       </c>
       <c r="E26" t="s">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
         <v>36</v>
@@ -2306,7 +2308,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>272</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
         <v>62</v>
@@ -2329,7 +2331,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
         <v>73</v>
@@ -2352,7 +2354,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
@@ -2374,7 +2376,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/tabela de habitat.xlsx
+++ b/tabela de habitat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_rebio23-mxr/mxr23_Q/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_09FA781D42CFBA99372140D0B83CDD583E7D1A6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6B82422-BFB9-42BE-AEFC-4956D10ACF0E}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_09FA781D42CFBA99372140D0B83CDD583E7D1A6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AF68791-9160-4605-8C91-8DD12F452096}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,8 +893,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -910,6 +913,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1804,9 +1811,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1924,9 +1933,11 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -2090,9 +2101,11 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -2141,9 +2154,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>128</v>
       </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -2376,6 +2391,12 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/tabela de habitat.xlsx
+++ b/tabela de habitat.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="tabela_final" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tabela_final" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -494,11 +488,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -507,26 +501,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -538,7 +516,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -546,49 +524,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="left" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -768,1056 +717,1055 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="0" t="s">
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="0" t="s">
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="0" t="s">
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="0" t="s">
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="0" t="s">
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" t="s">
         <v>101</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" t="s">
         <v>106</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" t="s">
         <v>110</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="0" t="s">
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="0" t="s">
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" t="s">
         <v>115</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="0" t="s">
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
         <v>98</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="0" t="s">
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" t="s">
         <v>115</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" ht="12.8" customHeight="1"/>
+    <row r="1048575" ht="12.8" customHeight="1"/>
+    <row r="1048576" ht="12.8" customHeight="1"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="s">
         <v>141</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="0" t="s">
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="s">
         <v>145</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="0" t="s">
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="0" t="s">
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="0" t="s">
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" t="s">
         <v>100</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" t="s">
         <v>81</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" t="s">
         <v>111</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" t="s">
         <v>119</v>
       </c>
-      <c r="F23" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="0" t="s">
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="0" t="s">
+      <c r="E25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" t="s">
         <v>115</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="G25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" ht="12.8" customHeight="1"/>
+    <row r="1048574" ht="12.8" customHeight="1"/>
+    <row r="1048575" ht="12.8" customHeight="1"/>
+    <row r="1048576" ht="12.8" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:C2"/>
@@ -1825,12 +1773,11 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A17:C17"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/tabela de habitat.xlsx
+++ b/tabela de habitat.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="tabela_final" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="tabela_final" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="156">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -488,11 +494,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -501,10 +507,26 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -516,7 +538,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -524,20 +546,49 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment textRotation="0" horizontal="left" vertical="bottom" indent="0"/>
-      <protection hidden="0" locked="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -717,1055 +768,1056 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <dimension ref="A1:G1048576"/>
+  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="0" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="0" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="0" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="E8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="0" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="0" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="0" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B13" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="0" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="F14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="0" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="F15" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="0" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="0" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="0" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="0" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="E19" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="0" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="s">
+      <c r="F20" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="0" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="B22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="E22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="0" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="1048574" ht="12.8" customHeight="1"/>
-    <row r="1048575" ht="12.8" customHeight="1"/>
-    <row r="1048576" ht="12.8" customHeight="1"/>
+    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <dimension ref="A1:G1048576"/>
+  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="0" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="0" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="0" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="0" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="E11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E11" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="0" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="0" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="B16" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="0" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="F18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="0" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="F19" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="0" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="0" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="0" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="0" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="s">
+      <c r="F23" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="0" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="E25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="E25" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="0" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="1048573" ht="12.8" customHeight="1"/>
-    <row r="1048574" ht="12.8" customHeight="1"/>
-    <row r="1048575" ht="12.8" customHeight="1"/>
-    <row r="1048576" ht="12.8" customHeight="1"/>
+    <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:C2"/>
@@ -1773,11 +1825,12 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A17:C17"/>
   </mergeCells>
-  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.634722222222222" bottom="0.634722222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>